--- a/artfynd/A 14946-2026 artfynd.xlsx
+++ b/artfynd/A 14946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56825596</v>
+        <v>56825595</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633463.8299952185</v>
+        <v>633314</v>
       </c>
       <c r="R2" t="n">
-        <v>7161612.973177527</v>
+        <v>7161817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,12 +785,7 @@
         <v>56825594</v>
       </c>
       <c r="B3" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633287.8021639311</v>
+        <v>633288</v>
       </c>
       <c r="R3" t="n">
-        <v>7161870.944917312</v>
+        <v>7161871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56825595</v>
+        <v>56825596</v>
       </c>
       <c r="B4" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633313.8831889505</v>
+        <v>633464</v>
       </c>
       <c r="R4" t="n">
-        <v>7161816.970553527</v>
+        <v>7161613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +957,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>björkstubbe</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1044,12 +999,7 @@
         <v>56825597</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633445.7890390047</v>
+        <v>633446</v>
       </c>
       <c r="R5" t="n">
-        <v>7161572.130359536</v>
+        <v>7161572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56825598</v>
+        <v>56825600</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633440.1037305139</v>
+        <v>633508</v>
       </c>
       <c r="R6" t="n">
-        <v>7161564.128934442</v>
+        <v>7161506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,21 +1171,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1192,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56825593</v>
+        <v>56825598</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633287.8021639311</v>
+        <v>633440</v>
       </c>
       <c r="R7" t="n">
-        <v>7161870.944917312</v>
+        <v>7161564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,21 +1278,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1299,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>gammal sälg</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1404,6 +1314,220 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>56825599</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lappmyran, Norra Spettlidenområdet, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633508</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7161506</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>56825593</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lappmyran, Norra Spettlidenområdet, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633288</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7161871</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gammal sälg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14946-2026 artfynd.xlsx
+++ b/artfynd/A 14946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825595</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825594</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825597</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825598</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825599</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,8 +1568,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>